--- a/budget/sola/sola-gk-budget.xlsx
+++ b/budget/sola/sola-gk-budget.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>135000</v>
+        <v>140000</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -1421,11 +1421,11 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Title Partner</t>
+          <t>Main Partner</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>4</v>
@@ -1449,13 +1449,13 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>15000</v>
+        <v>30000</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E6" s="7">
         <f>C6*D6</f>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>1</v>
@@ -1780,7 +1780,7 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>135000</v>
+        <v>140000</v>
       </c>
       <c r="B10" s="11">
         <f>Costs!E21</f>
